--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +48,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,16 +56,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -73,23 +93,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -100,18 +163,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela2" displayName="Tabela2" ref="A1:C11" totalsRowShown="0">
-  <autoFilter ref="A1:C11"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Usuario"/>
-    <tableColumn id="2" name="Senha "/>
-    <tableColumn id="3" name="Validade " dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,37 +431,32 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="3">
         <v>72714</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Usuario</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Master77</t>
+  </si>
+  <si>
+    <t>luiz</t>
   </si>
 </sst>
 </file>
@@ -134,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -148,6 +151,7 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -456,6 +460,17 @@
         <v>72714</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1234</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Usuario</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>Master77</t>
-  </si>
-  <si>
-    <t>luiz</t>
   </si>
 </sst>
 </file>
@@ -457,19 +454,11 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>72714</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1234</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46108</v>
-      </c>
+      <c r="C3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Usuario</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Master77</t>
+  </si>
+  <si>
+    <t>Luiz</t>
   </si>
 </sst>
 </file>
@@ -458,7 +461,15 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="7"/>
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1234</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46121</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Usuario</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Luiz</t>
+  </si>
+  <si>
+    <t>Data_de_Compra</t>
   </si>
 </sst>
 </file>
@@ -432,13 +435,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -448,8 +452,11 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -457,10 +464,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>46121</v>
+        <v>46274</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46116</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -468,7 +478,10 @@
         <v>1234</v>
       </c>
       <c r="C3" s="7">
-        <v>46121</v>
+        <v>46146</v>
+      </c>
+      <c r="D3" s="7">
+        <v>46116</v>
       </c>
     </row>
   </sheetData>

--- a/Usuarios.xlsx
+++ b/Usuarios.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Usuario</t>
   </si>
@@ -44,7 +44,10 @@
     <t>Luiz</t>
   </si>
   <si>
-    <t>Data_de_Compra</t>
+    <t>Data_Compra</t>
+  </si>
+  <si>
+    <t>luiz12</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -484,6 +487,20 @@
         <v>46116</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1234</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D4" s="7">
+        <v>46101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
